--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -12658,13 +12658,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="B1:C1"/>
     <mergeCell ref="AC1:AR1"/>
     <mergeCell ref="BM1:BN1"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="K1:T1"/>
     <mergeCell ref="AS1:BL1"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="U1:AA1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thali/Desktop/Perth_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2326265D-C7C5-E54D-A3CB-6361F57FAF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8313825-6E6F-974B-B48F-2701E8328A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1679,10 +1679,19 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1697,15 +1706,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2187,22 +2187,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="20"/>
     </row>
     <row r="4" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="20"/>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2280,10 +2280,10 @@
     <row r="78" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="79" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="82" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="28" t="s">
+      <c r="A82" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B82" s="21"/>
+      <c r="B82" s="20"/>
     </row>
     <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2361,10 +2361,10 @@
     <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="160" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A160" s="28" t="s">
+      <c r="A160" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B160" s="21"/>
+      <c r="B160" s="20"/>
     </row>
     <row r="161" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="162" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2442,10 +2442,10 @@
     <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="238" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A238" s="28" t="s">
+      <c r="A238" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B238" s="21"/>
+      <c r="B238" s="20"/>
     </row>
     <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2523,10 +2523,10 @@
     <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="313" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="316" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A316" s="28" t="s">
+      <c r="A316" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B316" s="21"/>
+      <c r="B316" s="20"/>
     </row>
     <row r="317" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="318" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2696,53 +2696,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:142" ht="56" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="21"/>
-      <c r="AL1" s="21"/>
-      <c r="AM1" s="21"/>
-      <c r="AN1" s="21"/>
-      <c r="AO1" s="21"/>
-      <c r="AS1" s="21"/>
-      <c r="AT1" s="21"/>
-      <c r="AU1" s="21"/>
-      <c r="AW1" s="21"/>
-      <c r="AX1" s="21"/>
-      <c r="AY1" s="21"/>
-      <c r="AZ1" s="21"/>
-      <c r="BA1" s="21"/>
-      <c r="BB1" s="21"/>
-      <c r="BC1" s="21"/>
-      <c r="BD1" s="21"/>
-      <c r="BE1" s="21"/>
-      <c r="BF1" s="21"/>
-      <c r="BG1" s="21"/>
-      <c r="BH1" s="21"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20"/>
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="20"/>
+      <c r="BH1" s="20"/>
       <c r="BN1" t="s">
         <v>7</v>
       </c>
@@ -2767,94 +2767,94 @@
       <c r="BU1" t="s">
         <v>14</v>
       </c>
-      <c r="BV1" s="21" t="s">
+      <c r="BV1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="BW1" s="21" t="s">
+      <c r="BW1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="BX1" s="21" t="s">
+      <c r="BX1" s="20" t="s">
         <v>476</v>
       </c>
       <c r="BY1" t="s">
         <v>16</v>
       </c>
-      <c r="BZ1" s="21" t="s">
+      <c r="BZ1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="CA1" s="21" t="s">
+      <c r="CA1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CB1" s="21" t="s">
+      <c r="CB1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CC1" s="21" t="s">
+      <c r="CC1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CD1" s="21" t="s">
+      <c r="CD1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="CE1" s="21" t="s">
+      <c r="CE1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CF1" s="21" t="s">
+      <c r="CF1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CG1" s="21" t="s">
+      <c r="CG1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CH1" s="21" t="s">
+      <c r="CH1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="CI1" s="21" t="s">
+      <c r="CI1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CJ1" s="21" t="s">
+      <c r="CJ1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CK1" s="21" t="s">
+      <c r="CK1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="CL1" s="21" t="s">
+      <c r="CL1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CM1" s="21" t="s">
+      <c r="CM1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CN1" s="21" t="s">
+      <c r="CN1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="CO1" s="21" t="s">
+      <c r="CO1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CP1" s="21" t="s">
+      <c r="CP1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CQ1" s="21" t="s">
+      <c r="CQ1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="CR1" s="21" t="s">
+      <c r="CR1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CS1" s="21" t="s">
+      <c r="CS1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CT1" s="21" t="s">
+      <c r="CT1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="CU1" s="21" t="s">
+      <c r="CU1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CV1" s="21" t="s">
+      <c r="CV1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CW1" s="21" t="s">
+      <c r="CW1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="CX1" s="21" t="s">
+      <c r="CX1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="CY1" s="21" t="s">
+      <c r="CY1" s="20" t="s">
         <v>476</v>
       </c>
       <c r="CZ1" t="s">
@@ -2863,52 +2863,52 @@
       <c r="DA1" t="s">
         <v>26</v>
       </c>
-      <c r="DB1" s="21" t="s">
+      <c r="DB1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="DC1" s="21" t="s">
+      <c r="DC1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DD1" s="21" t="s">
+      <c r="DD1" s="20" t="s">
         <v>476</v>
       </c>
       <c r="DE1" t="s">
         <v>28</v>
       </c>
-      <c r="DF1" s="21" t="s">
+      <c r="DF1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="DG1" s="21" t="s">
+      <c r="DG1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DH1" s="21" t="s">
+      <c r="DH1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DI1" s="21" t="s">
+      <c r="DI1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="DJ1" s="21" t="s">
+      <c r="DJ1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DK1" s="21" t="s">
+      <c r="DK1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DL1" s="21" t="s">
+      <c r="DL1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="DM1" s="21" t="s">
+      <c r="DM1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DN1" s="21" t="s">
+      <c r="DN1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DO1" s="21" t="s">
+      <c r="DO1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="DP1" s="21" t="s">
+      <c r="DP1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DQ1" s="21" t="s">
+      <c r="DQ1" s="20" t="s">
         <v>476</v>
       </c>
       <c r="DR1" t="s">
@@ -2926,49 +2926,49 @@
       <c r="DV1" t="s">
         <v>37</v>
       </c>
-      <c r="DW1" s="21" t="s">
+      <c r="DW1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="DX1" s="21" t="s">
+      <c r="DX1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DY1" s="21" t="s">
+      <c r="DY1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="DZ1" s="21" t="s">
+      <c r="DZ1" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="EA1" s="21" t="s">
+      <c r="EA1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EB1" s="21" t="s">
+      <c r="EB1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EC1" s="21" t="s">
+      <c r="EC1" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="ED1" s="21" t="s">
+      <c r="ED1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EE1" s="21" t="s">
+      <c r="EE1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EF1" s="21" t="s">
+      <c r="EF1" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="EG1" s="21" t="s">
+      <c r="EG1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EH1" s="21" t="s">
+      <c r="EH1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EI1" s="21" t="s">
+      <c r="EI1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="EJ1" s="21" t="s">
+      <c r="EJ1" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="EK1" s="21" t="s">
+      <c r="EK1" s="20" t="s">
         <v>476</v>
       </c>
       <c r="EL1" t="s">
@@ -3694,20 +3694,20 @@
       </c>
     </row>
     <row r="4" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="BN4" s="21" t="s">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="BN4" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="BO4" s="21" t="s">
+      <c r="BO4" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="BP4" s="21" t="s">
+      <c r="BP4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ4" s="21">
+      <c r="BQ4" s="20">
         <v>95</v>
       </c>
       <c r="BR4" t="s">
@@ -3931,20 +3931,20 @@
       </c>
     </row>
     <row r="5" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="BN5" s="21" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="BN5" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="BO5" s="21" t="s">
+      <c r="BO5" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="BP5" s="21" t="s">
+      <c r="BP5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ5" s="21">
+      <c r="BQ5" s="20">
         <v>95</v>
       </c>
       <c r="BR5" t="s">
@@ -4168,20 +4168,20 @@
       </c>
     </row>
     <row r="6" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="BN6" s="21" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="BN6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="BO6" s="21" t="s">
+      <c r="BO6" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="BP6" s="21" t="s">
+      <c r="BP6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ6" s="21">
+      <c r="BQ6" s="20">
         <v>94</v>
       </c>
       <c r="BR6" t="s">
@@ -4405,20 +4405,20 @@
       </c>
     </row>
     <row r="7" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="BN7" s="21" t="s">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="BN7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="BO7" s="21" t="s">
+      <c r="BO7" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="BP7" s="21" t="s">
+      <c r="BP7" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ7" s="21">
+      <c r="BQ7" s="20">
         <v>94</v>
       </c>
       <c r="BR7" t="s">
@@ -4642,20 +4642,20 @@
       </c>
     </row>
     <row r="8" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="BN8" s="21" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="BN8" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="BO8" s="21" t="s">
+      <c r="BO8" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="BP8" s="21" t="s">
+      <c r="BP8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ8" s="21">
+      <c r="BQ8" s="20">
         <v>95</v>
       </c>
       <c r="BR8" t="s">
@@ -4879,20 +4879,20 @@
       </c>
     </row>
     <row r="9" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="BN9" s="21" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="BN9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="BO9" s="21" t="s">
+      <c r="BO9" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="BP9" s="21" t="s">
+      <c r="BP9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ9" s="21">
+      <c r="BQ9" s="20">
         <v>95</v>
       </c>
       <c r="BR9" t="s">
@@ -5116,20 +5116,20 @@
       </c>
     </row>
     <row r="10" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="BN10" s="21" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="BN10" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="BO10" s="21" t="s">
+      <c r="BO10" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="BP10" s="21" t="s">
+      <c r="BP10" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ10" s="21">
+      <c r="BQ10" s="20">
         <v>93</v>
       </c>
       <c r="BR10" t="s">
@@ -5353,20 +5353,20 @@
       </c>
     </row>
     <row r="11" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="BN11" s="21" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="BN11" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="BO11" s="21" t="s">
+      <c r="BO11" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="BP11" s="21" t="s">
+      <c r="BP11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ11" s="21">
+      <c r="BQ11" s="20">
         <v>93</v>
       </c>
       <c r="BR11" t="s">
@@ -5590,20 +5590,20 @@
       </c>
     </row>
     <row r="12" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="BN12" s="21" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="BN12" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="BO12" s="21" t="s">
+      <c r="BO12" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="BP12" s="21" t="s">
+      <c r="BP12" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ12" s="21">
+      <c r="BQ12" s="20">
         <v>96</v>
       </c>
       <c r="BR12" t="s">
@@ -5827,20 +5827,20 @@
       </c>
     </row>
     <row r="13" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="BN13" s="21" t="s">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="BN13" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="BO13" s="21" t="s">
+      <c r="BO13" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="BP13" s="21" t="s">
+      <c r="BP13" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ13" s="21">
+      <c r="BQ13" s="20">
         <v>96</v>
       </c>
       <c r="BR13" t="s">
@@ -6064,20 +6064,20 @@
       </c>
     </row>
     <row r="14" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="BN14" s="21" t="s">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="BN14" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="BO14" s="21" t="s">
+      <c r="BO14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="BP14" s="21" t="s">
+      <c r="BP14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ14" s="21">
+      <c r="BQ14" s="20">
         <v>93</v>
       </c>
       <c r="BR14" t="s">
@@ -6301,20 +6301,20 @@
       </c>
     </row>
     <row r="15" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="BN15" s="21" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="BN15" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="BO15" s="21" t="s">
+      <c r="BO15" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="BP15" s="21" t="s">
+      <c r="BP15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ15" s="21">
+      <c r="BQ15" s="20">
         <v>93</v>
       </c>
       <c r="BR15" t="s">
@@ -6538,20 +6538,20 @@
       </c>
     </row>
     <row r="16" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="BN16" s="21" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="BN16" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="BO16" s="21" t="s">
+      <c r="BO16" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="BP16" s="21" t="s">
+      <c r="BP16" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ16" s="21">
+      <c r="BQ16" s="20">
         <v>99</v>
       </c>
       <c r="BR16" t="s">
@@ -6775,20 +6775,20 @@
       </c>
     </row>
     <row r="17" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="BN17" s="21" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="BN17" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="BO17" s="21" t="s">
+      <c r="BO17" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="BP17" s="21" t="s">
+      <c r="BP17" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ17" s="21">
+      <c r="BQ17" s="20">
         <v>99</v>
       </c>
       <c r="BR17" t="s">
@@ -7012,20 +7012,20 @@
       </c>
     </row>
     <row r="18" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="BN18" s="21" t="s">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="BN18" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="BO18" s="21" t="s">
+      <c r="BO18" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="BP18" s="21" t="s">
+      <c r="BP18" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ18" s="21">
+      <c r="BQ18" s="20">
         <v>95</v>
       </c>
       <c r="BR18" t="s">
@@ -7249,20 +7249,20 @@
       </c>
     </row>
     <row r="19" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="BN19" s="21" t="s">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="BN19" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="BO19" s="21" t="s">
+      <c r="BO19" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="BP19" s="21" t="s">
+      <c r="BP19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ19" s="21">
+      <c r="BQ19" s="20">
         <v>95</v>
       </c>
       <c r="BR19" t="s">
@@ -7486,20 +7486,20 @@
       </c>
     </row>
     <row r="20" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="BN20" s="21" t="s">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="BN20" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="BO20" s="21" t="s">
+      <c r="BO20" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="BP20" s="21" t="s">
+      <c r="BP20" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ20" s="21">
+      <c r="BQ20" s="20">
         <v>94</v>
       </c>
       <c r="BR20" t="s">
@@ -7723,20 +7723,20 @@
       </c>
     </row>
     <row r="21" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="BN21" s="21" t="s">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="BN21" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="BO21" s="21" t="s">
+      <c r="BO21" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="BP21" s="21" t="s">
+      <c r="BP21" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ21" s="21">
+      <c r="BQ21" s="20">
         <v>94</v>
       </c>
       <c r="BR21" t="s">
@@ -7960,20 +7960,20 @@
       </c>
     </row>
     <row r="22" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="BN22" s="21" t="s">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="BN22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="BO22" s="21" t="s">
+      <c r="BO22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="BP22" s="21" t="s">
+      <c r="BP22" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ22" s="21">
+      <c r="BQ22" s="20">
         <v>96</v>
       </c>
       <c r="BR22" t="s">
@@ -8197,20 +8197,20 @@
       </c>
     </row>
     <row r="23" spans="1:142" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="BN23" s="21" t="s">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="BN23" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="BO23" s="21" t="s">
+      <c r="BO23" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="BP23" s="21" t="s">
+      <c r="BP23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ23" s="21">
+      <c r="BQ23" s="20">
         <v>96</v>
       </c>
       <c r="BR23" t="s">
@@ -8434,16 +8434,16 @@
       </c>
     </row>
     <row r="24" spans="1:142" x14ac:dyDescent="0.15">
-      <c r="BN24" s="21" t="s">
+      <c r="BN24" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="BO24" s="21" t="s">
+      <c r="BO24" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="BP24" s="21" t="s">
+      <c r="BP24" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ24" s="21">
+      <c r="BQ24" s="20">
         <v>95</v>
       </c>
       <c r="BR24" t="s">
@@ -8667,16 +8667,16 @@
       </c>
     </row>
     <row r="25" spans="1:142" x14ac:dyDescent="0.15">
-      <c r="BN25" s="21" t="s">
+      <c r="BN25" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="BO25" s="21" t="s">
+      <c r="BO25" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="BP25" s="21" t="s">
+      <c r="BP25" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="BQ25" s="21">
+      <c r="BQ25" s="20">
         <v>95</v>
       </c>
       <c r="BR25" t="s">
@@ -8900,91 +8900,35 @@
       </c>
     </row>
     <row r="26" spans="1:142" x14ac:dyDescent="0.15">
-      <c r="BN26" s="21"/>
-      <c r="BO26" s="21"/>
-      <c r="BP26" s="21"/>
-      <c r="BQ26" s="21"/>
+      <c r="BN26" s="20"/>
+      <c r="BO26" s="20"/>
+      <c r="BP26" s="20"/>
+      <c r="BQ26" s="20"/>
     </row>
     <row r="27" spans="1:142" x14ac:dyDescent="0.15">
-      <c r="BN27" s="21"/>
-      <c r="BO27" s="21"/>
-      <c r="BP27" s="21"/>
-      <c r="BQ27" s="21"/>
+      <c r="BN27" s="20"/>
+      <c r="BO27" s="20"/>
+      <c r="BP27" s="20"/>
+      <c r="BQ27" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="BN26:BN27"/>
-    <mergeCell ref="BO26:BO27"/>
-    <mergeCell ref="BP26:BP27"/>
-    <mergeCell ref="BQ26:BQ27"/>
-    <mergeCell ref="BN22:BN23"/>
-    <mergeCell ref="BO22:BO23"/>
-    <mergeCell ref="BP22:BP23"/>
-    <mergeCell ref="BQ22:BQ23"/>
-    <mergeCell ref="BN24:BN25"/>
-    <mergeCell ref="BO24:BO25"/>
-    <mergeCell ref="BP24:BP25"/>
-    <mergeCell ref="BQ24:BQ25"/>
-    <mergeCell ref="BN18:BN19"/>
-    <mergeCell ref="BO18:BO19"/>
-    <mergeCell ref="BP18:BP19"/>
-    <mergeCell ref="BQ18:BQ19"/>
-    <mergeCell ref="BN20:BN21"/>
-    <mergeCell ref="BO20:BO21"/>
-    <mergeCell ref="BP20:BP21"/>
-    <mergeCell ref="BQ20:BQ21"/>
-    <mergeCell ref="BN14:BN15"/>
-    <mergeCell ref="BO14:BO15"/>
-    <mergeCell ref="BP14:BP15"/>
-    <mergeCell ref="BQ14:BQ15"/>
-    <mergeCell ref="BN16:BN17"/>
-    <mergeCell ref="BO16:BO17"/>
-    <mergeCell ref="BP16:BP17"/>
-    <mergeCell ref="BQ16:BQ17"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BN12:BN13"/>
-    <mergeCell ref="BO12:BO13"/>
-    <mergeCell ref="BP12:BP13"/>
-    <mergeCell ref="BQ12:BQ13"/>
-    <mergeCell ref="DZ1:EB1"/>
-    <mergeCell ref="EC1:EE1"/>
-    <mergeCell ref="EF1:EH1"/>
-    <mergeCell ref="EI1:EK1"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="DF1:DH1"/>
-    <mergeCell ref="DI1:DK1"/>
-    <mergeCell ref="DL1:DN1"/>
-    <mergeCell ref="DO1:DQ1"/>
-    <mergeCell ref="DW1:DY1"/>
-    <mergeCell ref="CN1:CP1"/>
-    <mergeCell ref="CQ1:CS1"/>
-    <mergeCell ref="CT1:CV1"/>
-    <mergeCell ref="CW1:CY1"/>
-    <mergeCell ref="DB1:DD1"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="BZ1:CC1"/>
-    <mergeCell ref="CD1:CG1"/>
-    <mergeCell ref="CH1:CJ1"/>
-    <mergeCell ref="CK1:CM1"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AW1:AY1"/>
-    <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="BN6:BN7"/>
-    <mergeCell ref="BO6:BO7"/>
-    <mergeCell ref="BP6:BP7"/>
-    <mergeCell ref="BQ6:BQ7"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="C16:C17"/>
@@ -9009,6 +8953,20 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AW1:AY1"/>
+    <mergeCell ref="AZ1:BB1"/>
+    <mergeCell ref="BN6:BN7"/>
+    <mergeCell ref="BO6:BO7"/>
+    <mergeCell ref="BP6:BP7"/>
+    <mergeCell ref="BQ6:BQ7"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="P1:S1"/>
     <mergeCell ref="X1:Z1"/>
@@ -9019,22 +8977,64 @@
     <mergeCell ref="BF1:BH1"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="EF1:EH1"/>
+    <mergeCell ref="EI1:EK1"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="DF1:DH1"/>
+    <mergeCell ref="DI1:DK1"/>
+    <mergeCell ref="DL1:DN1"/>
+    <mergeCell ref="DO1:DQ1"/>
+    <mergeCell ref="DW1:DY1"/>
+    <mergeCell ref="CN1:CP1"/>
+    <mergeCell ref="CQ1:CS1"/>
+    <mergeCell ref="CT1:CV1"/>
+    <mergeCell ref="CW1:CY1"/>
+    <mergeCell ref="DB1:DD1"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="BZ1:CC1"/>
+    <mergeCell ref="CD1:CG1"/>
+    <mergeCell ref="CH1:CJ1"/>
+    <mergeCell ref="CK1:CM1"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BN12:BN13"/>
+    <mergeCell ref="BO12:BO13"/>
+    <mergeCell ref="BP12:BP13"/>
+    <mergeCell ref="BQ12:BQ13"/>
+    <mergeCell ref="DZ1:EB1"/>
+    <mergeCell ref="EC1:EE1"/>
+    <mergeCell ref="BN18:BN19"/>
+    <mergeCell ref="BO18:BO19"/>
+    <mergeCell ref="BP18:BP19"/>
+    <mergeCell ref="BQ18:BQ19"/>
+    <mergeCell ref="BN20:BN21"/>
+    <mergeCell ref="BO20:BO21"/>
+    <mergeCell ref="BP20:BP21"/>
+    <mergeCell ref="BQ20:BQ21"/>
+    <mergeCell ref="BN14:BN15"/>
+    <mergeCell ref="BO14:BO15"/>
+    <mergeCell ref="BP14:BP15"/>
+    <mergeCell ref="BQ14:BQ15"/>
+    <mergeCell ref="BN16:BN17"/>
+    <mergeCell ref="BO16:BO17"/>
+    <mergeCell ref="BP16:BP17"/>
+    <mergeCell ref="BQ16:BQ17"/>
+    <mergeCell ref="BN26:BN27"/>
+    <mergeCell ref="BO26:BO27"/>
+    <mergeCell ref="BP26:BP27"/>
+    <mergeCell ref="BQ26:BQ27"/>
+    <mergeCell ref="BN22:BN23"/>
+    <mergeCell ref="BO22:BO23"/>
+    <mergeCell ref="BP22:BP23"/>
+    <mergeCell ref="BQ22:BQ23"/>
+    <mergeCell ref="BN24:BN25"/>
+    <mergeCell ref="BO24:BO25"/>
+    <mergeCell ref="BP24:BP25"/>
+    <mergeCell ref="BQ24:BQ25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9114,87 +9114,87 @@
       <c r="A1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="20"/>
+      <c r="D1" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="25" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="26" t="s">
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
       <c r="AB1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AC1" s="22" t="s">
+      <c r="AC1" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="21"/>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="21"/>
-      <c r="AL1" s="21"/>
-      <c r="AM1" s="21"/>
-      <c r="AN1" s="21"/>
-      <c r="AO1" s="21"/>
-      <c r="AP1" s="21"/>
-      <c r="AQ1" s="21"/>
-      <c r="AR1" s="21"/>
-      <c r="AS1" s="25" t="s">
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="AT1" s="21"/>
-      <c r="AU1" s="21"/>
-      <c r="AV1" s="21"/>
-      <c r="AW1" s="21"/>
-      <c r="AX1" s="21"/>
-      <c r="AY1" s="21"/>
-      <c r="AZ1" s="21"/>
-      <c r="BA1" s="21"/>
-      <c r="BB1" s="21"/>
-      <c r="BC1" s="21"/>
-      <c r="BD1" s="21"/>
-      <c r="BE1" s="21"/>
-      <c r="BF1" s="21"/>
-      <c r="BG1" s="21"/>
-      <c r="BH1" s="21"/>
-      <c r="BI1" s="21"/>
-      <c r="BJ1" s="21"/>
-      <c r="BK1" s="21"/>
-      <c r="BL1" s="21"/>
-      <c r="BM1" s="23" t="s">
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20"/>
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="20"/>
+      <c r="BH1" s="20"/>
+      <c r="BI1" s="20"/>
+      <c r="BJ1" s="20"/>
+      <c r="BK1" s="20"/>
+      <c r="BL1" s="20"/>
+      <c r="BM1" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="BN1" s="21"/>
+      <c r="BN1" s="20"/>
     </row>
     <row r="2" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">

--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thali/Desktop/Perth_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8313825-6E6F-974B-B48F-2701E8328A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AC054A-57C2-7641-9006-92E5C08C1A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8913,22 +8913,85 @@
     </row>
   </sheetData>
   <mergeCells count="122">
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="BN26:BN27"/>
+    <mergeCell ref="BO26:BO27"/>
+    <mergeCell ref="BP26:BP27"/>
+    <mergeCell ref="BQ26:BQ27"/>
+    <mergeCell ref="BN22:BN23"/>
+    <mergeCell ref="BO22:BO23"/>
+    <mergeCell ref="BP22:BP23"/>
+    <mergeCell ref="BQ22:BQ23"/>
+    <mergeCell ref="BN24:BN25"/>
+    <mergeCell ref="BO24:BO25"/>
+    <mergeCell ref="BP24:BP25"/>
+    <mergeCell ref="BQ24:BQ25"/>
+    <mergeCell ref="BN18:BN19"/>
+    <mergeCell ref="BO18:BO19"/>
+    <mergeCell ref="BP18:BP19"/>
+    <mergeCell ref="BQ18:BQ19"/>
+    <mergeCell ref="BN20:BN21"/>
+    <mergeCell ref="BO20:BO21"/>
+    <mergeCell ref="BP20:BP21"/>
+    <mergeCell ref="BQ20:BQ21"/>
+    <mergeCell ref="BN14:BN15"/>
+    <mergeCell ref="BO14:BO15"/>
+    <mergeCell ref="BP14:BP15"/>
+    <mergeCell ref="BQ14:BQ15"/>
+    <mergeCell ref="BN16:BN17"/>
+    <mergeCell ref="BO16:BO17"/>
+    <mergeCell ref="BP16:BP17"/>
+    <mergeCell ref="BQ16:BQ17"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BN12:BN13"/>
+    <mergeCell ref="BO12:BO13"/>
+    <mergeCell ref="BP12:BP13"/>
+    <mergeCell ref="BQ12:BQ13"/>
+    <mergeCell ref="DZ1:EB1"/>
+    <mergeCell ref="EC1:EE1"/>
+    <mergeCell ref="EF1:EH1"/>
+    <mergeCell ref="EI1:EK1"/>
+    <mergeCell ref="BN4:BN5"/>
+    <mergeCell ref="BO4:BO5"/>
+    <mergeCell ref="BP4:BP5"/>
+    <mergeCell ref="BQ4:BQ5"/>
+    <mergeCell ref="DF1:DH1"/>
+    <mergeCell ref="DI1:DK1"/>
+    <mergeCell ref="DL1:DN1"/>
+    <mergeCell ref="DO1:DQ1"/>
+    <mergeCell ref="DW1:DY1"/>
+    <mergeCell ref="CN1:CP1"/>
+    <mergeCell ref="CQ1:CS1"/>
+    <mergeCell ref="CT1:CV1"/>
+    <mergeCell ref="CW1:CY1"/>
+    <mergeCell ref="DB1:DD1"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="BZ1:CC1"/>
+    <mergeCell ref="CD1:CG1"/>
+    <mergeCell ref="CH1:CJ1"/>
+    <mergeCell ref="CK1:CM1"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="BC1:BE1"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="BF1:BH1"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AW1:AY1"/>
+    <mergeCell ref="AZ1:BB1"/>
+    <mergeCell ref="BN6:BN7"/>
+    <mergeCell ref="BO6:BO7"/>
+    <mergeCell ref="BP6:BP7"/>
+    <mergeCell ref="BQ6:BQ7"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="C16:C17"/>
@@ -8953,88 +9016,25 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AW1:AY1"/>
-    <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="BN6:BN7"/>
-    <mergeCell ref="BO6:BO7"/>
-    <mergeCell ref="BP6:BP7"/>
-    <mergeCell ref="BQ6:BQ7"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="BC1:BE1"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="BF1:BH1"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="EF1:EH1"/>
-    <mergeCell ref="EI1:EK1"/>
-    <mergeCell ref="BN4:BN5"/>
-    <mergeCell ref="BO4:BO5"/>
-    <mergeCell ref="BP4:BP5"/>
-    <mergeCell ref="BQ4:BQ5"/>
-    <mergeCell ref="DF1:DH1"/>
-    <mergeCell ref="DI1:DK1"/>
-    <mergeCell ref="DL1:DN1"/>
-    <mergeCell ref="DO1:DQ1"/>
-    <mergeCell ref="DW1:DY1"/>
-    <mergeCell ref="CN1:CP1"/>
-    <mergeCell ref="CQ1:CS1"/>
-    <mergeCell ref="CT1:CV1"/>
-    <mergeCell ref="CW1:CY1"/>
-    <mergeCell ref="DB1:DD1"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="BZ1:CC1"/>
-    <mergeCell ref="CD1:CG1"/>
-    <mergeCell ref="CH1:CJ1"/>
-    <mergeCell ref="CK1:CM1"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BN12:BN13"/>
-    <mergeCell ref="BO12:BO13"/>
-    <mergeCell ref="BP12:BP13"/>
-    <mergeCell ref="BQ12:BQ13"/>
-    <mergeCell ref="DZ1:EB1"/>
-    <mergeCell ref="EC1:EE1"/>
-    <mergeCell ref="BN18:BN19"/>
-    <mergeCell ref="BO18:BO19"/>
-    <mergeCell ref="BP18:BP19"/>
-    <mergeCell ref="BQ18:BQ19"/>
-    <mergeCell ref="BN20:BN21"/>
-    <mergeCell ref="BO20:BO21"/>
-    <mergeCell ref="BP20:BP21"/>
-    <mergeCell ref="BQ20:BQ21"/>
-    <mergeCell ref="BN14:BN15"/>
-    <mergeCell ref="BO14:BO15"/>
-    <mergeCell ref="BP14:BP15"/>
-    <mergeCell ref="BQ14:BQ15"/>
-    <mergeCell ref="BN16:BN17"/>
-    <mergeCell ref="BO16:BO17"/>
-    <mergeCell ref="BP16:BP17"/>
-    <mergeCell ref="BQ16:BQ17"/>
-    <mergeCell ref="BN26:BN27"/>
-    <mergeCell ref="BO26:BO27"/>
-    <mergeCell ref="BP26:BP27"/>
-    <mergeCell ref="BQ26:BQ27"/>
-    <mergeCell ref="BN22:BN23"/>
-    <mergeCell ref="BO22:BO23"/>
-    <mergeCell ref="BP22:BP23"/>
-    <mergeCell ref="BQ22:BQ23"/>
-    <mergeCell ref="BN24:BN25"/>
-    <mergeCell ref="BO24:BO25"/>
-    <mergeCell ref="BP24:BP25"/>
-    <mergeCell ref="BQ24:BQ25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -2241,12 +2241,12 @@
     <row r="4" ht="12" customHeight="1" s="21">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Balcatta - Perth 0:1</t>
+          <t>Perth - Fremantle City 2:1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2264,392 +2264,404 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="L4" t="n">
+        <v>283</v>
+      </c>
+      <c r="M4" t="n">
+        <v>181</v>
+      </c>
+      <c r="N4" t="n">
+        <v>63.96</v>
+      </c>
+      <c r="O4" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="P4" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>48</v>
+      </c>
+      <c r="S4" t="n">
+        <v>62</v>
+      </c>
+      <c r="T4" t="n">
+        <v>88</v>
+      </c>
+      <c r="U4" t="n">
+        <v>44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>238</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>125</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="AC4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>35</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>31</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>101</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>66</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>63</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>128</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>72</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>49</v>
+      </c>
+      <c r="BR4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>47</v>
-      </c>
-      <c r="P4" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>99</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="BS4" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX4" t="n">
         <v>32</v>
       </c>
-      <c r="S4" t="n">
-        <v>44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>23</v>
-      </c>
-      <c r="U4" t="n">
-        <v>213</v>
-      </c>
-      <c r="V4" t="n">
-        <v>99</v>
-      </c>
-      <c r="W4" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>43</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>24.21</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>74</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>77.03</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>52</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>163</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>91</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>57</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>84</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>45</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>53.57</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW4" t="n">
+      <c r="BY4" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>31</v>
       </c>
-      <c r="BX4" t="n">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>6.84</v>
+      <c r="CA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>8.85</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1" s="21">
       <c r="E5" t="inlineStr">
         <is>
-          <t>Balcatta</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4-2-3-1 (49.96%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="L5" t="n">
-        <v>55.43</v>
+        <v>44.57</v>
       </c>
       <c r="M5" t="n">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="n">
         <v>99</v>
       </c>
       <c r="R5" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="T5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="U5" t="n">
         <v>213</v>
       </c>
       <c r="V5" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="W5" t="n">
-        <v>51.17</v>
+        <v>46.48</v>
       </c>
       <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
         <v>3</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
       <c r="Z5" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.14</v>
+        <v>23.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AG5" t="n">
         <v>4</v>
       </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>41.67</v>
+        <v>13.33</v>
       </c>
       <c r="AM5" t="n">
         <v>6</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>24.21</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV5" t="n">
         <v>74</v>
       </c>
-      <c r="AP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>95</v>
-      </c>
       <c r="AW5" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="AX5" t="n">
-        <v>75.79000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="AY5" t="n">
         <v>18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.22</v>
+        <v>22.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BE5" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="BF5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="n">
         <v>1</v>
@@ -2658,241 +2670,223 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="BK5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="BL5" t="n">
-        <v>58.68</v>
+        <v>55.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="BN5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BO5" t="n">
-        <v>36.51</v>
+        <v>53.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="BQ5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BR5" t="n">
-        <v>51.02</v>
+        <v>50.88</v>
       </c>
       <c r="BS5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="BT5" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="BU5" t="n">
-        <v>42.05</v>
+        <v>53.57</v>
       </c>
       <c r="BV5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="BW5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="BX5" t="n">
-        <v>82.93000000000001</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="BY5" t="n">
-        <v>14.71</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="6" ht="12" customHeight="1" s="21">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Perth - West NTC 3:0</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Balcatta</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4-2-3-1 (49.96%)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>164</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37</v>
+      </c>
+      <c r="O6" t="n">
+        <v>71</v>
+      </c>
+      <c r="P6" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>99</v>
+      </c>
+      <c r="R6" t="n">
+        <v>48</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>213</v>
+      </c>
+      <c r="V6" t="n">
+        <v>109</v>
+      </c>
+      <c r="W6" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AV6" t="n">
         <v>95</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>4-1-3-2 (71.18%)</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="L6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>161</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="n">
-        <v>55</v>
-      </c>
-      <c r="P6" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>105</v>
-      </c>
-      <c r="R6" t="n">
-        <v>30</v>
-      </c>
-      <c r="S6" t="n">
-        <v>54</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21</v>
-      </c>
-      <c r="U6" t="n">
-        <v>168</v>
-      </c>
-      <c r="V6" t="n">
-        <v>78</v>
-      </c>
-      <c r="W6" t="n">
-        <v>46.43</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AW6" t="n">
+        <v>72</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>72.22</v>
+      </c>
+      <c r="BB6" t="n">
         <v>2</v>
       </c>
-      <c r="Z6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="AJ6" t="n">
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>39</v>
+      </c>
+      <c r="BF6" t="n">
         <v>18</v>
       </c>
-      <c r="AK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>33.82</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="BG6" t="n">
         <v>2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>79</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>49</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>43</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>14</v>
       </c>
       <c r="BH6" t="n">
         <v>1</v>
@@ -2901,301 +2895,283 @@
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="BK6" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="BL6" t="n">
-        <v>62.5</v>
+        <v>58.68</v>
       </c>
       <c r="BM6" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="BN6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BO6" t="n">
-        <v>38.03</v>
+        <v>36.51</v>
       </c>
       <c r="BP6" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="BQ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>88</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>37</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW6" t="n">
         <v>34</v>
       </c>
-      <c r="BR6" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>81</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>57</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>70.37</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>18</v>
-      </c>
       <c r="BX6" t="n">
-        <v>64.29000000000001</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.33</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="7" ht="12" customHeight="1" s="21">
       <c r="E7" t="inlineStr">
         <is>
-          <t>West NTC</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-3-2 (71.18%)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.45</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
       <c r="K7" t="n">
-        <v>28.57</v>
+        <v>30.43</v>
       </c>
       <c r="L7" t="n">
-        <v>40.8</v>
+        <v>59.2</v>
       </c>
       <c r="M7" t="n">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="N7" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="O7" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R7" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="U7" t="n">
         <v>168</v>
       </c>
       <c r="V7" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="W7" t="n">
-        <v>52.38</v>
+        <v>46.43</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
         <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>66.67</v>
+        <v>25</v>
       </c>
       <c r="AA7" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AG7" t="n">
         <v>6</v>
       </c>
-      <c r="AC7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN7" t="n">
         <v>27</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AO7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT7" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AU7" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="AV7" t="n">
         <v>79</v>
       </c>
-      <c r="AP7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>68</v>
-      </c>
       <c r="AW7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AX7" t="n">
-        <v>66.18000000000001</v>
+        <v>62.03</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BD7" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BF7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>200</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>125</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>71</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>27</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>81</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>81</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>57</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW7" t="n">
         <v>18</v>
       </c>
-      <c r="BG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>176</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>103</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>58.52</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>32.73</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>49</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>96</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>35</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>17</v>
-      </c>
       <c r="BX7" t="n">
-        <v>73.91</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>28.29</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1" s="21">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Perth - Sorrento 3:0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>94</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>West NTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3204,388 +3180,388 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="L8" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>173</v>
+      </c>
+      <c r="N8" t="n">
+        <v>47</v>
+      </c>
+      <c r="O8" t="n">
+        <v>75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>107</v>
+      </c>
+      <c r="R8" t="n">
+        <v>59</v>
+      </c>
+      <c r="S8" t="n">
+        <v>43</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>168</v>
+      </c>
+      <c r="V8" t="n">
+        <v>88</v>
+      </c>
+      <c r="W8" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="X8" t="n">
         <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="I8" t="n">
-        <v>31</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="L8" t="n">
-        <v>62.54</v>
-      </c>
-      <c r="M8" t="n">
-        <v>108</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>13</v>
-      </c>
-      <c r="P8" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>91</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>45</v>
-      </c>
-      <c r="U8" t="n">
-        <v>179</v>
-      </c>
-      <c r="V8" t="n">
-        <v>84</v>
-      </c>
-      <c r="W8" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="X8" t="n">
-        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>16.67</v>
+        <v>66.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="AB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD8" t="n">
         <v>27</v>
       </c>
-      <c r="AC8" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>13</v>
-      </c>
       <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AR8" t="n">
         <v>3</v>
       </c>
-      <c r="AF8" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AS8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>45</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="AY8" t="n">
         <v>8</v>
       </c>
-      <c r="AH8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AZ8" t="n">
         <v>7</v>
       </c>
-      <c r="AL8" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>31</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>58</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>81</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="BA8" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>176</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>103</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>58.52</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>49</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>96</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>35</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="BV8" t="n">
         <v>23</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>67</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>47</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>187</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>148</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>40</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>95</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>74</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>77.89</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>110</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>101</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>91.81999999999999</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>31</v>
-      </c>
       <c r="BW8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="BX8" t="n">
-        <v>93.55</v>
+        <v>73.91</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.51</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1" s="21">
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4-5-1 (100.0%)</t>
+          <t>4-4-2 (100.0%)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>19.35</v>
       </c>
       <c r="L9" t="n">
-        <v>37.46</v>
+        <v>62.54</v>
       </c>
       <c r="M9" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="N9" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="R9" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="U9" t="n">
         <v>179</v>
       </c>
       <c r="V9" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="W9" t="n">
-        <v>51.96</v>
+        <v>46.93</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>24.14</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="AO9" t="n">
+        <v>81</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>67</v>
       </c>
-      <c r="AP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>29.03</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>81</v>
-      </c>
       <c r="AW9" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AX9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AY9" t="n">
         <v>7</v>
       </c>
       <c r="AZ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF9" t="n">
         <v>2</v>
       </c>
-      <c r="BA9" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>49</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>12</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -3594,466 +3570,448 @@
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>114</v>
+        <v>187</v>
       </c>
       <c r="BK9" t="n">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="BL9" t="n">
-        <v>43.86</v>
+        <v>79.14</v>
       </c>
       <c r="BM9" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BN9" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BO9" t="n">
-        <v>22.92</v>
+        <v>65</v>
       </c>
       <c r="BP9" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="BR9" t="n">
-        <v>40</v>
+        <v>77.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="BT9" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.75</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="BV9" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.18</v>
+        <v>93.55</v>
       </c>
       <c r="BY9" t="n">
-        <v>122.5</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="10" ht="12" customHeight="1" s="21">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Subiaco - Perth 0:5</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>95</v>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4-2-3-1 (100.0%)</t>
+          <t>4-5-1 (100.0%)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="M10" t="n">
+        <v>140</v>
+      </c>
+      <c r="N10" t="n">
+        <v>63</v>
+      </c>
+      <c r="O10" t="n">
+        <v>61</v>
+      </c>
+      <c r="P10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
-        <v>13</v>
-      </c>
-      <c r="K10" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="L10" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="M10" t="n">
-        <v>137</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
+        <v>75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>68</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>179</v>
+      </c>
+      <c r="V10" t="n">
+        <v>93</v>
+      </c>
+      <c r="W10" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP10" t="n">
         <v>20</v>
       </c>
-      <c r="O10" t="n">
+      <c r="AQ10" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>81</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>58</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>49</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>114</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="BM10" t="n">
         <v>48</v>
       </c>
-      <c r="P10" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>105</v>
-      </c>
-      <c r="R10" t="n">
-        <v>39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>44</v>
-      </c>
-      <c r="T10" t="n">
-        <v>22</v>
-      </c>
-      <c r="U10" t="n">
-        <v>242</v>
-      </c>
-      <c r="V10" t="n">
-        <v>126</v>
-      </c>
-      <c r="W10" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="BN10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>6</v>
       </c>
-      <c r="Y10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="BR10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>80</v>
+      </c>
+      <c r="BT10" t="n">
         <v>11</v>
       </c>
-      <c r="AC10" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="BU10" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BV10" t="n">
         <v>17</v>
       </c>
-      <c r="AE10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="BW10" t="n">
         <v>7</v>
       </c>
-      <c r="AN10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>99</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>37</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>86</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>67</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>160</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>106</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>67</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>37</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>82</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>49</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>59.76</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>29</v>
-      </c>
       <c r="BX10" t="n">
-        <v>85.29000000000001</v>
+        <v>41.18</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.92</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1" s="21">
       <c r="E11" t="inlineStr">
         <is>
-          <t>Subiaco</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4-3-3 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.13</v>
+        <v>2.25</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>137</v>
+      </c>
+      <c r="N11" t="n">
         <v>20</v>
       </c>
-      <c r="L11" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>164</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
+        <v>48</v>
+      </c>
+      <c r="P11" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>105</v>
+      </c>
+      <c r="R11" t="n">
         <v>39</v>
       </c>
-      <c r="O11" t="n">
-        <v>58</v>
-      </c>
-      <c r="P11" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>89</v>
-      </c>
-      <c r="R11" t="n">
-        <v>41</v>
-      </c>
       <c r="S11" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="T11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="U11" t="n">
         <v>242</v>
       </c>
       <c r="V11" t="n">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="W11" t="n">
-        <v>44.21</v>
+        <v>52.07</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>83.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.79</v>
+        <v>23.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
-        <v>4.17</v>
+        <v>29.41</v>
       </c>
       <c r="AG11" t="n">
         <v>5</v>
       </c>
       <c r="AH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>1</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AU11" t="n">
         <v>20</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="AV11" t="n">
         <v>86</v>
       </c>
-      <c r="AP11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>24.42</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>99</v>
-      </c>
       <c r="AW11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AX11" t="n">
-        <v>62.63</v>
+        <v>75.58</v>
       </c>
       <c r="AY11" t="n">
         <v>25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
       </c>
       <c r="BC11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="BF11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="n">
         <v>2</v>
@@ -4062,466 +4020,448 @@
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="BK11" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="BL11" t="n">
-        <v>50.69</v>
+        <v>66.25</v>
       </c>
       <c r="BM11" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="BN11" t="n">
         <v>37</v>
       </c>
       <c r="BO11" t="n">
-        <v>46.84</v>
+        <v>55.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BQ11" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BR11" t="n">
-        <v>54.76</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="BT11" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="BU11" t="n">
-        <v>44.44</v>
+        <v>59.76</v>
       </c>
       <c r="BV11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BX11" t="n">
-        <v>68.56999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.960000000000001</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1" s="21">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>West NTC - Perth 0:1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>93</v>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Subiaco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-3-3 (100.0%)</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>164</v>
+      </c>
+      <c r="N12" t="n">
+        <v>39</v>
+      </c>
+      <c r="O12" t="n">
+        <v>58</v>
+      </c>
+      <c r="P12" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>41</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
+        <v>242</v>
+      </c>
+      <c r="V12" t="n">
+        <v>107</v>
+      </c>
+      <c r="W12" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>50</v>
-      </c>
-      <c r="L12" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="M12" t="n">
-        <v>176</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="Z12" t="n">
         <v>25</v>
       </c>
-      <c r="O12" t="n">
-        <v>63</v>
-      </c>
-      <c r="P12" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>121</v>
-      </c>
-      <c r="R12" t="n">
-        <v>32</v>
-      </c>
-      <c r="S12" t="n">
-        <v>63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>26</v>
-      </c>
-      <c r="U12" t="n">
-        <v>221</v>
-      </c>
-      <c r="V12" t="n">
-        <v>124</v>
-      </c>
-      <c r="W12" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB12" t="n">
         <v>4</v>
       </c>
-      <c r="Z12" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>41</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>10</v>
       </c>
       <c r="AK12" t="n">
         <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AP12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>99</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>62</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="AY12" t="n">
         <v>25</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>30.49</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>77.27</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>19</v>
       </c>
       <c r="AZ12" t="n">
         <v>9</v>
       </c>
       <c r="BA12" t="n">
-        <v>47.37</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI12" t="n">
         <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="BK12" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="BL12" t="n">
-        <v>61.5</v>
+        <v>50.69</v>
       </c>
       <c r="BM12" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="BN12" t="n">
+        <v>37</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>23</v>
       </c>
-      <c r="BO12" t="n">
-        <v>38.98</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>73</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>38</v>
-      </c>
       <c r="BR12" t="n">
-        <v>52.05</v>
+        <v>54.76</v>
       </c>
       <c r="BS12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BT12" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="BU12" t="n">
-        <v>59.49</v>
+        <v>44.44</v>
       </c>
       <c r="BV12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="BW12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BX12" t="n">
-        <v>65.91</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.74</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="21">
       <c r="E13" t="inlineStr">
         <is>
-          <t>West NTC</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
         <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>35.87</v>
+        <v>64.13</v>
       </c>
       <c r="M13" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="N13" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O13" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="P13" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="Q13" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="R13" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="U13" t="n">
         <v>221</v>
       </c>
       <c r="V13" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="W13" t="n">
-        <v>42.08</v>
+        <v>56.11</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2</v>
       </c>
-      <c r="Z13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>1</v>
       </c>
       <c r="AL13" t="n">
-        <v>16.67</v>
+        <v>10</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AN13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22.73</v>
+        <v>30.49</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AV13" t="n">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AW13" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="AX13" t="n">
-        <v>69.51000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="AY13" t="n">
         <v>19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
-        <v>42.11</v>
+        <v>47.37</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="BE13" t="n">
         <v>62</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -4530,466 +4470,448 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="BK13" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="BL13" t="n">
-        <v>45.11</v>
+        <v>61.5</v>
       </c>
       <c r="BM13" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="BN13" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BO13" t="n">
-        <v>32.65</v>
+        <v>38.98</v>
       </c>
       <c r="BP13" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="BQ13" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BR13" t="n">
-        <v>43.24</v>
+        <v>52.05</v>
       </c>
       <c r="BS13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="BT13" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="BU13" t="n">
-        <v>28.38</v>
+        <v>59.49</v>
       </c>
       <c r="BV13" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>65.91</v>
       </c>
       <c r="BY13" t="n">
-        <v>18.32</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="21">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Perth - Perth RedStar 1:1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>96</v>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>West NTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-4-2 (100.0%)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.38</v>
+        <v>0.38</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>45.86</v>
+        <v>35.87</v>
       </c>
       <c r="M14" t="n">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="N14" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="P14" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="Q14" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="R14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="S14" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="T14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U14" t="n">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="V14" t="n">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="W14" t="n">
-        <v>54.44</v>
+        <v>42.08</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
         <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
         <v>7</v>
       </c>
-      <c r="AC14" t="n">
-        <v>25.93</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>18</v>
-      </c>
       <c r="AO14" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AP14" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>23.68</v>
+        <v>22.73</v>
       </c>
       <c r="AR14" t="n">
         <v>1</v>
       </c>
       <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT14" t="n">
         <v>6</v>
       </c>
-      <c r="AT14" t="n">
-        <v>1</v>
-      </c>
       <c r="AU14" t="n">
-        <v>16.67</v>
+        <v>50</v>
       </c>
       <c r="AV14" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="AW14" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="AX14" t="n">
-        <v>79.06999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
-        <v>33.33</v>
+        <v>42.11</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
+        <v>62</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>133</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>49</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>37</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>74</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="BV14" t="n">
         <v>51</v>
       </c>
-      <c r="BF14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>161</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>105</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>65</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>27</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>61</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>81</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>53</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>65.43000000000001</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>26</v>
-      </c>
       <c r="BW14" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BX14" t="n">
-        <v>65.38</v>
+        <v>58.82</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.16</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1" s="21">
       <c r="E15" t="inlineStr">
         <is>
-          <t>Perth RedStar</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>1.38</v>
       </c>
       <c r="I15" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" t="n">
         <v>6</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" t="n">
-        <v>16.67</v>
+        <v>54.55</v>
       </c>
       <c r="L15" t="n">
-        <v>54.14</v>
+        <v>45.86</v>
       </c>
       <c r="M15" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="P15" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="Q15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="R15" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="S15" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="T15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
         <v>259</v>
       </c>
       <c r="V15" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="W15" t="n">
-        <v>44.79</v>
+        <v>54.44</v>
       </c>
       <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE15" t="n">
         <v>3</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2</v>
-      </c>
       <c r="AF15" t="n">
-        <v>9.52</v>
+        <v>15.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH15" t="n">
         <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AL15" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AP15" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20.93</v>
+        <v>23.68</v>
       </c>
       <c r="AR15" t="n">
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
-        <v>54.55</v>
+        <v>16.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="AW15" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="AX15" t="n">
-        <v>76.31999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="AY15" t="n">
         <v>33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>63.64</v>
+        <v>33.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BD15" t="n">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="BE15" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BF15" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="n">
         <v>1</v>
@@ -4998,466 +4920,448 @@
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="BK15" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="BL15" t="n">
-        <v>62.58</v>
+        <v>65.22</v>
       </c>
       <c r="BM15" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="BN15" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BO15" t="n">
-        <v>39.22</v>
+        <v>41.54</v>
       </c>
       <c r="BP15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BR15" t="n">
-        <v>53.45</v>
+        <v>52.46</v>
       </c>
       <c r="BS15" t="n">
         <v>81</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="BU15" t="n">
-        <v>61.73</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="BV15" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="BW15" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="BX15" t="n">
-        <v>82.86</v>
+        <v>65.38</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.69</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1" s="21">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>UWA Nedlands - Perth 1:3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>93</v>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Perth RedStar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4-3-3 (100.0%)</t>
+          <t>4-4-2 (100.0%)</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="L16" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="M16" t="n">
+        <v>157</v>
+      </c>
+      <c r="N16" t="n">
+        <v>21</v>
+      </c>
+      <c r="O16" t="n">
+        <v>68</v>
+      </c>
+      <c r="P16" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>105</v>
+      </c>
+      <c r="R16" t="n">
+        <v>44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>46</v>
+      </c>
+      <c r="T16" t="n">
+        <v>15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>259</v>
+      </c>
+      <c r="V16" t="n">
+        <v>116</v>
+      </c>
+      <c r="W16" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="X16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I16" t="n">
-        <v>17</v>
-      </c>
-      <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="L16" t="n">
-        <v>52</v>
-      </c>
-      <c r="M16" t="n">
-        <v>113</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
         <v>10</v>
       </c>
-      <c r="O16" t="n">
-        <v>41</v>
-      </c>
-      <c r="P16" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>92</v>
-      </c>
-      <c r="R16" t="n">
-        <v>29</v>
-      </c>
-      <c r="S16" t="n">
-        <v>39</v>
-      </c>
-      <c r="T16" t="n">
-        <v>24</v>
-      </c>
-      <c r="U16" t="n">
-        <v>203</v>
-      </c>
-      <c r="V16" t="n">
-        <v>106</v>
-      </c>
-      <c r="W16" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AD16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" t="n">
         <v>7</v>
       </c>
-      <c r="Y16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>27.27</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>31.03</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>28</v>
-      </c>
       <c r="AO16" t="n">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="AP16" t="n">
         <v>27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>36.99</v>
+        <v>20.93</v>
       </c>
       <c r="AR16" t="n">
         <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU16" t="n">
-        <v>100</v>
+        <v>54.55</v>
       </c>
       <c r="AV16" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AW16" t="n">
         <v>58</v>
       </c>
       <c r="AX16" t="n">
-        <v>72.5</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>52.63</v>
+        <v>63.64</v>
       </c>
       <c r="BB16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH16" t="n">
         <v>1</v>
       </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
       <c r="BI16" t="n">
         <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="BK16" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="BL16" t="n">
-        <v>59.06</v>
+        <v>62.58</v>
       </c>
       <c r="BM16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BN16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BO16" t="n">
-        <v>43.4</v>
+        <v>39.22</v>
       </c>
       <c r="BP16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="BQ16" t="n">
+        <v>31</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>81</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW16" t="n">
         <v>29</v>
       </c>
-      <c r="BR16" t="n">
-        <v>51.79</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>84</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>51</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>41</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>36</v>
-      </c>
       <c r="BX16" t="n">
-        <v>87.8</v>
+        <v>82.86</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.2</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1" s="21">
       <c r="E17" t="inlineStr">
         <is>
-          <t>UWA Nedlands</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4-2-3-1 (100.0%)</t>
+          <t>4-3-3 (100.0%)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.23</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>47.06</v>
       </c>
       <c r="L17" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="N17" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q17" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="R17" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="U17" t="n">
         <v>203</v>
       </c>
       <c r="V17" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="W17" t="n">
-        <v>45.81</v>
+        <v>52.22</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
       </c>
       <c r="Z17" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>73</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU17" t="n">
         <v>100</v>
       </c>
-      <c r="AA17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO17" t="n">
+      <c r="AV17" t="n">
         <v>80</v>
       </c>
-      <c r="AP17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>73</v>
-      </c>
       <c r="AW17" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="AX17" t="n">
-        <v>63.01</v>
+        <v>72.5</v>
       </c>
       <c r="AY17" t="n">
         <v>19</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA17" t="n">
-        <v>47.37</v>
+        <v>52.63</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BF17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -5466,385 +5370,367 @@
         <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="BK17" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="BL17" t="n">
-        <v>56.03</v>
+        <v>59.06</v>
       </c>
       <c r="BM17" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="BN17" t="n">
         <v>23</v>
       </c>
       <c r="BO17" t="n">
-        <v>40.35</v>
+        <v>43.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="BQ17" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BR17" t="n">
-        <v>52.27</v>
+        <v>51.79</v>
       </c>
       <c r="BS17" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="BT17" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="BU17" t="n">
-        <v>50</v>
+        <v>60.71</v>
       </c>
       <c r="BV17" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="BW17" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BX17" t="n">
-        <v>70.97</v>
+        <v>87.8</v>
       </c>
       <c r="BY17" t="n">
-        <v>11.41</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1" s="21">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Perth - Balcatta 0:0</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>99</v>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>UWA Nedlands</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.24</v>
+        <v>0.23</v>
       </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>30.77</v>
+        <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>39.92</v>
+        <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="N18" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="P18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="R18" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="S18" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="V18" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="W18" t="n">
-        <v>49</v>
+        <v>45.81</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE18" t="n">
         <v>2</v>
       </c>
-      <c r="Z18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1</v>
       </c>
-      <c r="AF18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>8</v>
-      </c>
       <c r="AL18" t="n">
-        <v>47.06</v>
+        <v>10</v>
       </c>
       <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
         <v>3</v>
       </c>
-      <c r="AN18" t="n">
-        <v>16</v>
-      </c>
       <c r="AO18" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="n">
         <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>32.35</v>
+        <v>27.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>73</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>63.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="BB18" t="n">
         <v>4</v>
       </c>
-      <c r="AU18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>83</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>56</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
         <v>60</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>181</v>
+        <v>116</v>
       </c>
       <c r="BK18" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="BL18" t="n">
-        <v>59.67</v>
+        <v>56.03</v>
       </c>
       <c r="BM18" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="BN18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BO18" t="n">
-        <v>38.57</v>
+        <v>40.35</v>
       </c>
       <c r="BP18" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="BQ18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BR18" t="n">
-        <v>51.02</v>
+        <v>52.27</v>
       </c>
       <c r="BS18" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="BT18" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BU18" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BV18" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="BW18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BX18" t="n">
-        <v>78.26000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.02</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1" s="21">
       <c r="E19" t="inlineStr">
         <is>
-          <t>Balcatta</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4-4-1-1 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.73</v>
+        <v>1.24</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>40</v>
+        <v>30.77</v>
       </c>
       <c r="L19" t="n">
-        <v>60.08</v>
+        <v>39.92</v>
       </c>
       <c r="M19" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="N19" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="O19" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="Q19" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="R19" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="S19" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="T19" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="U19" t="n">
         <v>200</v>
       </c>
       <c r="V19" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W19" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
         <v>5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>41</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>4</v>
@@ -5856,58 +5742,58 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL19" t="n">
-        <v>20</v>
+        <v>47.06</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AP19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>32.53</v>
+        <v>32.35</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>30.77</v>
+        <v>40</v>
       </c>
       <c r="AV19" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="AW19" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="AX19" t="n">
-        <v>67.65000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="AY19" t="n">
         <v>16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
-        <v>56.25</v>
+        <v>37.5</v>
       </c>
       <c r="BB19" t="n">
         <v>0</v>
@@ -5919,1660 +5805,1588 @@
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BI19" t="n">
         <v>0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BK19" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BL19" t="n">
-        <v>58.15</v>
+        <v>59.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="BN19" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BO19" t="n">
-        <v>35.85</v>
+        <v>38.57</v>
       </c>
       <c r="BP19" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="BQ19" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BR19" t="n">
-        <v>54.29</v>
+        <v>51.02</v>
       </c>
       <c r="BS19" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="BT19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="BU19" t="n">
-        <v>58.33</v>
+        <v>52.17</v>
       </c>
       <c r="BV19" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="BW19" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BX19" t="n">
-        <v>91.43000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BY19" t="n">
-        <v>12.58</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1" s="21">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Perth - Fremantle City 0:0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>95</v>
-      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Balcatta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4-2-3-1 (48.4%)</t>
+          <t>4-4-1-1 (100.0%)</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="I20" t="n">
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L20" t="n">
-        <v>51.92</v>
+        <v>60.08</v>
       </c>
       <c r="M20" t="n">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="N20" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="O20" t="n">
+        <v>52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>104</v>
+      </c>
+      <c r="R20" t="n">
+        <v>41</v>
+      </c>
+      <c r="S20" t="n">
         <v>53</v>
       </c>
-      <c r="P20" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>97</v>
-      </c>
-      <c r="R20" t="n">
-        <v>54</v>
-      </c>
-      <c r="S20" t="n">
-        <v>32</v>
-      </c>
       <c r="T20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="V20" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="W20" t="n">
-        <v>50.29</v>
+        <v>49.5</v>
       </c>
       <c r="X20" t="n">
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="n">
-        <v>29.03</v>
+        <v>14.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AK20" t="n">
         <v>4</v>
       </c>
       <c r="AL20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU20" t="n">
         <v>30.77</v>
       </c>
-      <c r="AM20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>57</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>35.09</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
       <c r="AV20" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="AW20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>33</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>184</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>107</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>53</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>70</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>84</v>
+      </c>
+      <c r="BT20" t="n">
         <v>49</v>
       </c>
-      <c r="AX20" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>18.18</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>172</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>64.53</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>54</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>23</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>42.59</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>61</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>29</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>71</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>51</v>
-      </c>
       <c r="BU20" t="n">
-        <v>71.83</v>
+        <v>58.33</v>
       </c>
       <c r="BV20" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="BW20" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BX20" t="n">
-        <v>84.20999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="BY20" t="n">
-        <v>10.93</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1" s="21">
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fremantle City</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4-2-3-1 (100.0%)</t>
+          <t>4-2-3-1 (48.4%)</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>48.08</v>
+        <v>51.92</v>
       </c>
       <c r="M21" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="O21" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="P21" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="Q21" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="R21" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="S21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U21" t="n">
         <v>173</v>
       </c>
       <c r="V21" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="W21" t="n">
-        <v>46.82</v>
+        <v>50.29</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AB21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AM21" t="n">
         <v>5</v>
       </c>
-      <c r="AC21" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AN21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP21" t="n">
         <v>20</v>
       </c>
-      <c r="AE21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO21" t="n">
+      <c r="AQ21" t="n">
+        <v>35.09</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>77</v>
       </c>
-      <c r="AP21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>57</v>
-      </c>
       <c r="AW21" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AX21" t="n">
-        <v>64.91</v>
+        <v>63.64</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BA21" t="n">
-        <v>72.73</v>
+        <v>18.18</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE21" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="BF21" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="BG21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BH21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI21" t="n">
         <v>0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="BK21" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL21" t="n">
-        <v>65.84999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="BM21" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="BN21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>61</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>71</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>51</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>71.83</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW21" t="n">
         <v>16</v>
       </c>
-      <c r="BO21" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>60</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>33</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>68</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>43</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>63.24</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>33</v>
-      </c>
       <c r="BX21" t="n">
-        <v>78.56999999999999</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BY21" t="n">
-        <v>14.72</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1" s="21">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Sorrento - Perth 0:2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>94</v>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Fremantle City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84</v>
+        <v>0.39</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>26.67</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>59.94</v>
+        <v>48.08</v>
       </c>
       <c r="M22" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="O22" t="n">
         <v>35</v>
       </c>
       <c r="P22" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="Q22" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="R22" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="S22" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="T22" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="V22" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="W22" t="n">
-        <v>61.11</v>
+        <v>46.82</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="AB22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="AC22" t="n">
-        <v>41.07</v>
+        <v>15.15</v>
       </c>
       <c r="AD22" t="n">
         <v>20</v>
       </c>
       <c r="AE22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="n">
         <v>5</v>
       </c>
-      <c r="AF22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>57</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>37</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>8</v>
       </c>
-      <c r="AH22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>79</v>
-      </c>
-      <c r="AP22" t="n">
+      <c r="BA22" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>37</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>164</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ22" t="n">
         <v>33</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>41.77</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>76.47</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>77.78</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>165</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>120</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>72.73</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>39</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>46.15</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>78</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>54</v>
-      </c>
       <c r="BR22" t="n">
-        <v>69.23</v>
+        <v>55</v>
       </c>
       <c r="BS22" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="BT22" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="BU22" t="n">
-        <v>77.55</v>
+        <v>63.24</v>
       </c>
       <c r="BV22" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BW22" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="BX22" t="n">
-        <v>76</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY22" t="n">
-        <v>4.37</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1" s="21">
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4-5-1 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="L23" t="n">
-        <v>40.06</v>
+        <v>59.94</v>
       </c>
       <c r="M23" t="n">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="N23" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="P23" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="Q23" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="R23" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="U23" t="n">
         <v>198</v>
       </c>
       <c r="V23" t="n">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="W23" t="n">
-        <v>37.37</v>
+        <v>61.11</v>
       </c>
       <c r="X23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y23" t="n">
         <v>4</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="AB23" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AC23" t="n">
-        <v>31.58</v>
+        <v>41.07</v>
       </c>
       <c r="AD23" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL23" t="n">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
       <c r="AM23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AN23" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>33</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="AV23" t="n">
         <v>85</v>
       </c>
-      <c r="AP23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>23.53</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>79</v>
-      </c>
       <c r="AW23" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AX23" t="n">
-        <v>58.23</v>
+        <v>76.47</v>
       </c>
       <c r="AY23" t="n">
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>11.11</v>
+        <v>77.78</v>
       </c>
       <c r="BB23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC23" t="n">
         <v>1</v>
       </c>
       <c r="BD23" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BE23" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BG23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI23" t="n">
         <v>0</v>
       </c>
       <c r="BJ23" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="BK23" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="BL23" t="n">
-        <v>61.44</v>
+        <v>72.73</v>
       </c>
       <c r="BM23" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BN23" t="n">
         <v>18</v>
       </c>
       <c r="BO23" t="n">
-        <v>45</v>
+        <v>46.15</v>
       </c>
       <c r="BP23" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="BQ23" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="BR23" t="n">
-        <v>54.17</v>
+        <v>69.23</v>
       </c>
       <c r="BS23" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="BT23" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="BU23" t="n">
-        <v>31.17</v>
+        <v>77.55</v>
       </c>
       <c r="BV23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW23" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="BY23" t="n">
-        <v>13.46</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Perth - Subiaco 2:0</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>96</v>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4-2-3-1 (100.0%)</t>
+          <t>4-5-1 (100.0%)</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I24" t="n">
-        <v>18</v>
-      </c>
-      <c r="J24" t="n">
-        <v>8</v>
-      </c>
       <c r="K24" t="n">
-        <v>44.44</v>
+        <v>28.57</v>
       </c>
       <c r="L24" t="n">
-        <v>50.98</v>
+        <v>40.06</v>
       </c>
       <c r="M24" t="n">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="N24" t="n">
         <v>38</v>
       </c>
       <c r="O24" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="P24" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="Q24" t="n">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="R24" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S24" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="V24" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="W24" t="n">
-        <v>47.65</v>
+        <v>37.37</v>
       </c>
       <c r="X24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>9</v>
       </c>
-      <c r="Y24" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>41</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>36.59</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AK24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="AR24" t="n">
         <v>2</v>
       </c>
-      <c r="AF24" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AS24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>79</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>1</v>
       </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>67</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>23.88</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT24" t="n">
+      <c r="BA24" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="BB24" t="n">
         <v>3</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>73.33</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1</v>
       </c>
       <c r="BC24" t="n">
         <v>1</v>
       </c>
       <c r="BD24" t="n">
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="BE24" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="BF24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI24" t="n">
         <v>0</v>
       </c>
       <c r="BJ24" t="n">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="BK24" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="BL24" t="n">
-        <v>60.33</v>
+        <v>61.44</v>
       </c>
       <c r="BM24" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BN24" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BO24" t="n">
+        <v>45</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>77</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX24" t="n">
         <v>50</v>
       </c>
-      <c r="BP24" t="n">
-        <v>78</v>
-      </c>
-      <c r="BQ24" t="n">
-        <v>37</v>
-      </c>
-      <c r="BR24" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="BS24" t="n">
-        <v>110</v>
-      </c>
-      <c r="BT24" t="n">
-        <v>65</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>59.09</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>76.92</v>
-      </c>
       <c r="BY24" t="n">
-        <v>5.18</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="25">
       <c r="E25" t="inlineStr">
         <is>
-          <t>Subiaco</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4-4-2 (49.52%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>44.44</v>
       </c>
       <c r="L25" t="n">
-        <v>49.02</v>
+        <v>50.98</v>
       </c>
       <c r="M25" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="N25" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="O25" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="P25" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="Q25" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="R25" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="S25" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="T25" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="U25" t="n">
         <v>170</v>
       </c>
       <c r="V25" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="W25" t="n">
-        <v>51.76</v>
+        <v>47.65</v>
       </c>
       <c r="X25" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AM25" t="n">
         <v>8</v>
       </c>
-      <c r="Y25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>33</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>24.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>21.21</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AN25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
         <v>15</v>
       </c>
-      <c r="AK25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO25" t="n">
+      <c r="AT25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV25" t="n">
         <v>75</v>
       </c>
-      <c r="AP25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>67</v>
-      </c>
       <c r="AW25" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
-        <v>76.12</v>
+        <v>73.33</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA25" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG25" t="n">
         <v>5</v>
       </c>
-      <c r="BC25" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE25" t="n">
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>184</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>44</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>22</v>
+      </c>
+      <c r="BO25" t="n">
         <v>50</v>
       </c>
-      <c r="BF25" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>170</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>102</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>60</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>54</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>59.26</v>
-      </c>
       <c r="BP25" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="BQ25" t="n">
+        <v>37</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>110</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW25" t="n">
         <v>30</v>
       </c>
-      <c r="BR25" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>89</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>33</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>28</v>
-      </c>
       <c r="BX25" t="n">
-        <v>84.84999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="BY25" t="n">
-        <v>10.47</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Perth - UWA Nedlands 6:0</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>95</v>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Perth</t>
+          <t>Subiaco</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4-3-3 (100.0%)</t>
+          <t>4-4-2 (49.52%)</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="I26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
         <v>20</v>
       </c>
-      <c r="J26" t="n">
-        <v>11</v>
-      </c>
-      <c r="K26" t="n">
-        <v>55</v>
-      </c>
       <c r="L26" t="n">
-        <v>62.41</v>
+        <v>49.02</v>
       </c>
       <c r="M26" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O26" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="P26" t="n">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="Q26" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R26" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="S26" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="U26" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="V26" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="W26" t="n">
-        <v>50.32</v>
+        <v>51.76</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>46.15</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="AB26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AC26" t="n">
-        <v>25.37</v>
+        <v>24.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="AE26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>23.08</v>
+        <v>21.21</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
-        <v>28.57</v>
+        <v>57.14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AL26" t="n">
-        <v>27.59</v>
+        <v>33.33</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AO26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>38.57</v>
+        <v>26.67</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="AV26" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="AW26" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="AX26" t="n">
-        <v>70.37</v>
+        <v>76.12</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>54.55</v>
+        <v>60</v>
       </c>
       <c r="BB26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BD26" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="BE26" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="BF26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG26" t="n">
         <v>4</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
@@ -7581,205 +7395,205 @@
         <v>0</v>
       </c>
       <c r="BJ26" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="BK26" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="BL26" t="n">
-        <v>75.56</v>
+        <v>60</v>
       </c>
       <c r="BM26" t="n">
+        <v>54</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>32</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>59.26</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>57</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>89</v>
+      </c>
+      <c r="BT26" t="n">
         <v>46</v>
       </c>
-      <c r="BN26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>78</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>52</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>75</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>67</v>
-      </c>
       <c r="BU26" t="n">
-        <v>89.33</v>
+        <v>51.69</v>
       </c>
       <c r="BV26" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BW26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BX26" t="n">
-        <v>90.63</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.74</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="27">
       <c r="E27" t="inlineStr">
         <is>
-          <t>UWA Nedlands</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3-5-2 (100.0%)</t>
+          <t>4-3-3 (100.0%)</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>1.77</v>
       </c>
       <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>55</v>
+      </c>
+      <c r="L27" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="M27" t="n">
+        <v>132</v>
+      </c>
+      <c r="N27" t="n">
         <v>4</v>
       </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>50</v>
-      </c>
-      <c r="L27" t="n">
-        <v>37.59</v>
-      </c>
-      <c r="M27" t="n">
-        <v>126</v>
-      </c>
-      <c r="N27" t="n">
-        <v>43</v>
-      </c>
       <c r="O27" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="P27" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="Q27" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="R27" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="U27" t="n">
         <v>155</v>
       </c>
       <c r="V27" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="W27" t="n">
-        <v>47.74</v>
+        <v>50.32</v>
       </c>
       <c r="X27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
         <v>4</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AT27" t="n">
         <v>2</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AU27" t="n">
         <v>50</v>
       </c>
-      <c r="AA27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO27" t="n">
+      <c r="AV27" t="n">
         <v>54</v>
       </c>
-      <c r="AP27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>29.63</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>70</v>
-      </c>
       <c r="AW27" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="AX27" t="n">
-        <v>61.43</v>
+        <v>70.37</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA27" t="n">
-        <v>36.36</v>
+        <v>54.55</v>
       </c>
       <c r="BB27" t="n">
         <v>1</v>
@@ -7791,71 +7605,293 @@
         <v>100</v>
       </c>
       <c r="BE27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>180</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>136</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>46</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>78</v>
+      </c>
+      <c r="BQ27" t="n">
         <v>52</v>
       </c>
-      <c r="BF27" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>132</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>73</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>56</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>27</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>13</v>
-      </c>
       <c r="BR27" t="n">
-        <v>52</v>
+        <v>66.67</v>
       </c>
       <c r="BS27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BT27" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="BU27" t="n">
-        <v>28.57</v>
+        <v>89.33</v>
       </c>
       <c r="BV27" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="BW27" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BX27" t="n">
-        <v>78.56999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="BY27" t="n">
-        <v>22.31</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>UWA Nedlands</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>3-5-2 (100.0%)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>50</v>
+      </c>
+      <c r="L28" t="n">
+        <v>37.59</v>
+      </c>
+      <c r="M28" t="n">
+        <v>126</v>
+      </c>
+      <c r="N28" t="n">
+        <v>43</v>
+      </c>
+      <c r="O28" t="n">
+        <v>62</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" t="n">
+        <v>48</v>
+      </c>
+      <c r="S28" t="n">
+        <v>31</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>155</v>
+      </c>
+      <c r="V28" t="n">
+        <v>74</v>
+      </c>
+      <c r="W28" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>54</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>43</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>52</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>132</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>73</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>56</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>27</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>52</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>22.31</v>
+      </c>
     </row>
     <row r="29"/>
   </sheetData>
@@ -13515,11 +13551,11 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B1:C1"/>
     <mergeCell ref="AC1:AR1"/>
+    <mergeCell ref="K1:T1"/>
     <mergeCell ref="BM1:BN1"/>
     <mergeCell ref="D1:J1"/>
-    <mergeCell ref="K1:T1"/>
+    <mergeCell ref="B1:C1"/>
     <mergeCell ref="AS1:BL1"/>
     <mergeCell ref="U1:AA1"/>
   </mergeCells>
@@ -13533,7 +13569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="17.5" customWidth="1" style="21" min="2" max="2"/>
@@ -15909,6 +15945,99 @@
         <v>51.17</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Perth - Fremantle City 2:1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Australia. Western Australia NPL Women</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4-2-3-1 (100.0%)</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J26" t="n">
+        <v>14</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>283</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>181</v>
+      </c>
+      <c r="R26" t="n">
+        <v>63</v>
+      </c>
+      <c r="S26" t="n">
+        <v>37</v>
+      </c>
+      <c r="T26" t="n">
+        <v>127</v>
+      </c>
+      <c r="U26" t="n">
+        <v>17</v>
+      </c>
+      <c r="V26" t="n">
+        <v>48</v>
+      </c>
+      <c r="W26" t="n">
+        <v>62</v>
+      </c>
+      <c r="X26" t="n">
+        <v>88</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8008,63 +8008,63 @@
         <v>28.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>63.96</v>
       </c>
       <c r="P2" t="n">
-        <v>283</v>
+        <v>37.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="R2" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="T2" t="n">
+        <v>62</v>
+      </c>
+      <c r="U2" t="n">
+        <v>88</v>
+      </c>
+      <c r="V2" t="n">
+        <v>44</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>237</v>
+      </c>
+      <c r="Z2" t="n">
         <v>126</v>
       </c>
-      <c r="U2" t="n">
-        <v>16</v>
-      </c>
-      <c r="V2" t="n">
-        <v>48</v>
-      </c>
-      <c r="W2" t="n">
-        <v>62</v>
-      </c>
-      <c r="X2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>30</v>
-      </c>
       <c r="AA2" t="n">
-        <v>14</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Perth - Fremantle City 2:1</t>
+          <t>Balcatta - Perth 0:1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8073,91 +8073,91 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fremantle City</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.24</v>
+        <v>0.66</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>46.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>68.03</v>
       </c>
       <c r="P3" t="n">
-        <v>464</v>
+        <v>44.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>364</v>
+        <v>136</v>
       </c>
       <c r="R3" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="S3" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="T3" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="U3" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="V3" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="W3" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="X3" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>34</v>
+        <v>215</v>
       </c>
       <c r="Z3" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>17</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Balcatta - Perth 0:1</t>
+          <t>Perth - West NTC 3:0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8175,82 +8175,82 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>2.37</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>46.15</v>
+        <v>30.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>79.77</v>
       </c>
       <c r="P4" t="n">
-        <v>366</v>
+        <v>59.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="R4" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="T4" t="n">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="V4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="W4" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="X4" t="n">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Balcatta - Perth 0:1</t>
+          <t>Perth - Sorrento 3:0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8259,91 +8259,91 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Perth</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4-4-2 (100.0%)</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="M5" t="n">
+        <v>559</v>
+      </c>
+      <c r="N5" t="n">
+        <v>467</v>
+      </c>
+      <c r="O5" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="P5" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>108</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" t="n">
         <v>91</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Balcatta</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4-2-3-1 (49.96%)</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="V5" t="n">
         <v>8</v>
       </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>50</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>416</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>295</v>
-      </c>
-      <c r="R5" t="n">
-        <v>70</v>
-      </c>
-      <c r="S5" t="n">
-        <v>55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>164</v>
-      </c>
-      <c r="U5" t="n">
-        <v>36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>72</v>
-      </c>
       <c r="W5" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="X5" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="Y5" t="n">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="Z5" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Perth - West NTC 3:0</t>
+          <t>Subiaco - Perth 0:5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8365,78 +8365,78 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="J6" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>30.43</v>
+        <v>81.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>70.48</v>
       </c>
       <c r="P6" t="n">
-        <v>613</v>
+        <v>55.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="R6" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="S6" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="T6" t="n">
-        <v>160</v>
+        <v>69</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="V6" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="W6" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="X6" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>52.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perth - West NTC 3:0</t>
+          <t>West NTC - Perth 0:1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8445,91 +8445,91 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West NTC</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>28.57</v>
+        <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>401</v>
+        <v>64.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="R7" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="T7" t="n">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="U7" t="n">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="V7" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="W7" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="X7" t="n">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Perth - Sorrento 3:0</t>
+          <t>Perth - Perth RedStar 1:1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -8547,82 +8547,82 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.37</v>
+        <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>19.35</v>
+        <v>54.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>559</v>
+        <v>45.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>467</v>
+        <v>155</v>
       </c>
       <c r="R8" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="S8" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="T8" t="n">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="W8" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="X8" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="Z8" t="n">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="AA8" t="n">
-        <v>45</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perth - Sorrento 3:0</t>
+          <t>UWA Nedlands - Perth 1:3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8631,91 +8631,91 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4-5-1 (100.0%)</t>
+          <t>4-3-3 (100.0%)</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>47.06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>68.31</v>
       </c>
       <c r="P9" t="n">
-        <v>284</v>
+        <v>52</v>
       </c>
       <c r="Q9" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>41</v>
+      </c>
+      <c r="T9" t="n">
         <v>62</v>
       </c>
-      <c r="S9" t="n">
-        <v>37</v>
-      </c>
-      <c r="T9" t="n">
-        <v>140</v>
-      </c>
       <c r="U9" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="V9" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="X9" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Subiaco - Perth 0:5</t>
+          <t>Perth - Balcatta 0:0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -8733,82 +8733,82 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4-2-3-1 (100.0%)</t>
+          <t>4-1-4-1 (100.0%)</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.25</v>
+        <v>1.24</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>81.25</v>
+        <v>30.77</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>71.87</v>
       </c>
       <c r="P10" t="n">
-        <v>376</v>
+        <v>39.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="R10" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="S10" t="n">
+        <v>60</v>
+      </c>
+      <c r="T10" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" t="n">
+        <v>115</v>
+      </c>
+      <c r="V10" t="n">
         <v>55</v>
       </c>
-      <c r="T10" t="n">
-        <v>137</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" t="n">
-        <v>48</v>
-      </c>
       <c r="W10" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>39</v>
+        <v>200</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Subiaco - Perth 0:5</t>
+          <t>Perth - Fremantle City 0:0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8821,87 +8821,87 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Subiaco</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4-3-3 (100.0%)</t>
+          <t>4-2-3-1 (48.4%)</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>80.62</v>
       </c>
       <c r="P11" t="n">
-        <v>328</v>
+        <v>51.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="R11" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="S11" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="T11" t="n">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="U11" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="V11" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="W11" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="X11" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="AA11" t="n">
-        <v>12</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West NTC - Perth 0:1</t>
+          <t>Sorrento - Perth 0:2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -8923,78 +8923,78 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.84</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>26.67</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>78.81</v>
       </c>
       <c r="P12" t="n">
-        <v>596</v>
+        <v>59.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>453</v>
+        <v>112</v>
       </c>
       <c r="R12" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="T12" t="n">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="V12" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="W12" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="X12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>198</v>
+      </c>
+      <c r="Z12" t="n">
         <v>121</v>
       </c>
-      <c r="Y12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>63</v>
-      </c>
       <c r="AA12" t="n">
-        <v>26</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>West NTC - Perth 0:1</t>
+          <t>Perth - Subiaco 2:0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9003,91 +9003,91 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>West NTC</t>
+          <t>Perth</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4-4-2 (100.0%)</t>
+          <t>4-2-3-1 (100.0%)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.38</v>
+        <v>1.74</v>
       </c>
       <c r="J13" t="n">
+        <v>18</v>
+      </c>
+      <c r="K13" t="n">
         <v>8</v>
       </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>311</v>
+        <v>50.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="T13" t="n">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="V13" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="W13" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="X13" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="AA13" t="n">
-        <v>12</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Perth - Perth RedStar 1:1</t>
+          <t>Perth - UWA Nedlands 6:0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -9105,1277 +9105,68 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4-1-4-1 (100.0%)</t>
+          <t>4-3-3 (100.0%)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="n">
         <v>11</v>
       </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
       <c r="L14" t="n">
-        <v>54.55</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>386</v>
+        <v>62.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="R14" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="T14" t="n">
+        <v>101</v>
+      </c>
+      <c r="U14" t="n">
+        <v>95</v>
+      </c>
+      <c r="V14" t="n">
+        <v>19</v>
+      </c>
+      <c r="W14" t="n">
+        <v>44</v>
+      </c>
+      <c r="X14" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y14" t="n">
         <v>155</v>
       </c>
-      <c r="U14" t="n">
-        <v>19</v>
-      </c>
-      <c r="V14" t="n">
-        <v>60</v>
-      </c>
-      <c r="W14" t="n">
-        <v>76</v>
-      </c>
-      <c r="X14" t="n">
-        <v>120</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>47</v>
-      </c>
       <c r="Z14" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Perth - Perth RedStar 1:1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>96</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Perth RedStar</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4-4-2 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>315</v>
-      </c>
-      <c r="R15" t="n">
-        <v>75</v>
-      </c>
-      <c r="S15" t="n">
-        <v>54</v>
-      </c>
-      <c r="T15" t="n">
-        <v>157</v>
-      </c>
-      <c r="U15" t="n">
-        <v>21</v>
-      </c>
-      <c r="V15" t="n">
-        <v>68</v>
-      </c>
-      <c r="W15" t="n">
-        <v>68</v>
-      </c>
-      <c r="X15" t="n">
-        <v>105</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>UWA Nedlands - Perth 1:3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>93</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4-3-3 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>366</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>250</v>
-      </c>
-      <c r="R16" t="n">
-        <v>68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>52</v>
-      </c>
-      <c r="T16" t="n">
-        <v>113</v>
-      </c>
-      <c r="U16" t="n">
-        <v>10</v>
-      </c>
-      <c r="V16" t="n">
-        <v>41</v>
-      </c>
-      <c r="W16" t="n">
-        <v>62</v>
-      </c>
-      <c r="X16" t="n">
-        <v>92</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UWA Nedlands - Perth 1:3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>93</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UWA Nedlands</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4-2-3-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>100</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>281</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>185</v>
-      </c>
-      <c r="R17" t="n">
-        <v>65</v>
-      </c>
-      <c r="S17" t="n">
-        <v>48</v>
-      </c>
-      <c r="T17" t="n">
-        <v>150</v>
-      </c>
-      <c r="U17" t="n">
-        <v>33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>67</v>
-      </c>
-      <c r="W17" t="n">
-        <v>50</v>
-      </c>
-      <c r="X17" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Perth - Balcatta 0:0</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>99</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4-1-4-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>391</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>281</v>
-      </c>
-      <c r="R18" t="n">
-        <v>71</v>
-      </c>
-      <c r="S18" t="n">
-        <v>39</v>
-      </c>
-      <c r="T18" t="n">
-        <v>137</v>
-      </c>
-      <c r="U18" t="n">
-        <v>17</v>
-      </c>
-      <c r="V18" t="n">
-        <v>60</v>
-      </c>
-      <c r="W18" t="n">
-        <v>60</v>
-      </c>
-      <c r="X18" t="n">
-        <v>115</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Perth - Balcatta 0:0</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>99</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Balcatta</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4-4-1-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>40</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>503</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>371</v>
-      </c>
-      <c r="R19" t="n">
-        <v>73</v>
-      </c>
-      <c r="S19" t="n">
-        <v>60</v>
-      </c>
-      <c r="T19" t="n">
-        <v>162</v>
-      </c>
-      <c r="U19" t="n">
-        <v>31</v>
-      </c>
-      <c r="V19" t="n">
-        <v>52</v>
-      </c>
-      <c r="W19" t="n">
-        <v>79</v>
-      </c>
-      <c r="X19" t="n">
-        <v>104</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Perth - Fremantle City 0:0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>95</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4-2-3-1 (48.4%)</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>30</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>516</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>416</v>
-      </c>
-      <c r="R20" t="n">
-        <v>80</v>
-      </c>
-      <c r="S20" t="n">
-        <v>51</v>
-      </c>
-      <c r="T20" t="n">
-        <v>128</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18</v>
-      </c>
-      <c r="V20" t="n">
-        <v>53</v>
-      </c>
-      <c r="W20" t="n">
-        <v>57</v>
-      </c>
-      <c r="X20" t="n">
-        <v>97</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Perth - Fremantle City 0:0</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>95</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Fremantle City</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4-2-3-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J21" t="n">
-        <v>8</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>417</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>314</v>
-      </c>
-      <c r="R21" t="n">
-        <v>75</v>
-      </c>
-      <c r="S21" t="n">
-        <v>48</v>
-      </c>
-      <c r="T21" t="n">
-        <v>144</v>
-      </c>
-      <c r="U21" t="n">
-        <v>26</v>
-      </c>
-      <c r="V21" t="n">
-        <v>35</v>
-      </c>
-      <c r="W21" t="n">
-        <v>83</v>
-      </c>
-      <c r="X21" t="n">
-        <v>79</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sorrento - Perth 0:2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>94</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>4-1-4-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J22" t="n">
-        <v>30</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>372</v>
-      </c>
-      <c r="R22" t="n">
-        <v>78</v>
-      </c>
-      <c r="S22" t="n">
-        <v>59</v>
-      </c>
-      <c r="T22" t="n">
-        <v>112</v>
-      </c>
-      <c r="U22" t="n">
-        <v>10</v>
-      </c>
-      <c r="V22" t="n">
-        <v>35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>67</v>
-      </c>
-      <c r="X22" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sorrento - Perth 0:2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>94</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sorrento</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4-5-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>316</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>221</v>
-      </c>
-      <c r="R23" t="n">
-        <v>69</v>
-      </c>
-      <c r="S23" t="n">
-        <v>40</v>
-      </c>
-      <c r="T23" t="n">
-        <v>134</v>
-      </c>
-      <c r="U23" t="n">
-        <v>38</v>
-      </c>
-      <c r="V23" t="n">
-        <v>68</v>
-      </c>
-      <c r="W23" t="n">
-        <v>28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Perth - Subiaco 2:0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>96</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>4-2-3-1 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>429</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>308</v>
-      </c>
-      <c r="R24" t="n">
-        <v>71</v>
-      </c>
-      <c r="S24" t="n">
-        <v>50</v>
-      </c>
-      <c r="T24" t="n">
-        <v>167</v>
-      </c>
-      <c r="U24" t="n">
-        <v>38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>51</v>
-      </c>
-      <c r="W24" t="n">
-        <v>78</v>
-      </c>
-      <c r="X24" t="n">
-        <v>106</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Perth - Subiaco 2:0</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>96</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Subiaco</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>4-4-2 (49.52%)</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J25" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>20</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>260</v>
-      </c>
-      <c r="R25" t="n">
-        <v>68</v>
-      </c>
-      <c r="S25" t="n">
-        <v>49</v>
-      </c>
-      <c r="T25" t="n">
-        <v>154</v>
-      </c>
-      <c r="U25" t="n">
-        <v>21</v>
-      </c>
-      <c r="V25" t="n">
-        <v>68</v>
-      </c>
-      <c r="W25" t="n">
-        <v>65</v>
-      </c>
-      <c r="X25" t="n">
-        <v>94</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Perth - UWA Nedlands 6:0</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>95</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Perth</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>4-3-3 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="J26" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" t="n">
-        <v>11</v>
-      </c>
-      <c r="L26" t="n">
-        <v>55</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>514</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>411</v>
-      </c>
-      <c r="R26" t="n">
-        <v>79</v>
-      </c>
-      <c r="S26" t="n">
-        <v>62</v>
-      </c>
-      <c r="T26" t="n">
-        <v>132</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>27</v>
-      </c>
-      <c r="W26" t="n">
-        <v>101</v>
-      </c>
-      <c r="X26" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Perth - UWA Nedlands 6:0</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Australia. Western Australia NPL Women</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>95</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>UWA Nedlands</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>3-5-2 (100.0%)</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>50</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>319</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>229</v>
-      </c>
-      <c r="R27" t="n">
-        <v>71</v>
-      </c>
-      <c r="S27" t="n">
-        <v>37</v>
-      </c>
-      <c r="T27" t="n">
-        <v>126</v>
-      </c>
-      <c r="U27" t="n">
-        <v>43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>62</v>
-      </c>
-      <c r="W27" t="n">
-        <v>21</v>
-      </c>
-      <c r="X27" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>31</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1</v>
+        <v>50.32</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_perth.xlsx
+++ b/team_stats_perth.xlsx
@@ -8626,7 +8626,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
